--- a/40_数据库/学习笔记_连接工具_DBeaver.xlsx
+++ b/40_数据库/学习笔记_连接工具_DBeaver.xlsx
@@ -1,34 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B72812-8960-44C8-B495-B262A5623C13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="8"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概述" sheetId="1" r:id="rId1"/>
     <sheet name="安装" sheetId="2" r:id="rId2"/>
     <sheet name="基础" sheetId="10" r:id="rId3"/>
-    <sheet name="语法" sheetId="5" r:id="rId4"/>
-    <sheet name="知识点" sheetId="3" r:id="rId5"/>
-    <sheet name="示例" sheetId="6" r:id="rId6"/>
-    <sheet name="重点" sheetId="9" r:id="rId7"/>
-    <sheet name="总结" sheetId="4" r:id="rId8"/>
-    <sheet name="问题" sheetId="8" r:id="rId9"/>
-    <sheet name="参考" sheetId="7" r:id="rId10"/>
+    <sheet name="导出导入" sheetId="11" r:id="rId4"/>
+    <sheet name="语法" sheetId="5" r:id="rId5"/>
+    <sheet name="知识点" sheetId="3" r:id="rId6"/>
+    <sheet name="示例" sheetId="6" r:id="rId7"/>
+    <sheet name="重点" sheetId="9" r:id="rId8"/>
+    <sheet name="总结" sheetId="4" r:id="rId9"/>
+    <sheet name="问题" sheetId="8" r:id="rId10"/>
+    <sheet name="参考" sheetId="7" r:id="rId11"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <r>
       <rPr>
@@ -149,12 +154,44 @@
     <t>知识点内容</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>Dbeaver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dbeaver支持跨库导出导入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>即将一个库的表数据，导入到别外的表。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>默认的导入导出配置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>导入时修改配置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不自动生成列</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>启用多行插入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提高效率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -203,6 +240,42 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -245,7 +318,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -264,6 +337,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -293,7 +370,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -307,6 +384,221 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>100537</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DDB5914-4BBE-4935-B56D-7C4FC46EDC8D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="666750" y="900637"/>
+          <a:ext cx="8191500" cy="6090713"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="190500" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="70000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>44802</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63C09848-5E72-4617-83E0-4BFF3B8BF665}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="8648700" y="8131527"/>
+          <a:ext cx="9677400" cy="5079648"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="190500" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="70000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>609908</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3554EA34-6B5B-418D-A25D-980D421B7036}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="666750" y="8162925"/>
+          <a:ext cx="7486958" cy="4829175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw blurRad="190500" algn="tl" rotWithShape="0">
+            <a:srgbClr val="000000">
+              <a:alpha val="70000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -564,17 +856,23 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -582,9 +880,20 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -592,9 +901,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -602,9 +911,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -612,30 +921,75 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4CD61A6-959C-4AA8-BC74-0BE9499DAB0E}">
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B4" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="B41" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C42" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C43" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.375" customWidth="1"/>
     <col min="5" max="5" width="53" customWidth="1"/>
-    <col min="6" max="6" width="45.21875" customWidth="1"/>
-    <col min="7" max="7" width="63.6640625" customWidth="1"/>
-    <col min="8" max="8" width="24.88671875" customWidth="1"/>
+    <col min="6" max="6" width="45.25" customWidth="1"/>
+    <col min="7" max="7" width="63.625" customWidth="1"/>
+    <col min="8" max="8" width="24.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -661,7 +1015,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -673,7 +1027,7 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -685,7 +1039,7 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -697,7 +1051,7 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -709,7 +1063,7 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -721,7 +1075,7 @@
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -733,7 +1087,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -745,7 +1099,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -757,7 +1111,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -769,7 +1123,7 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -781,7 +1135,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -793,7 +1147,7 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -805,7 +1159,7 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -817,7 +1171,7 @@
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -829,7 +1183,7 @@
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -841,7 +1195,7 @@
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -853,7 +1207,7 @@
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -865,7 +1219,7 @@
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -877,7 +1231,7 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -889,7 +1243,7 @@
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -901,7 +1255,7 @@
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -913,7 +1267,7 @@
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -925,7 +1279,7 @@
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -937,7 +1291,7 @@
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -949,7 +1303,7 @@
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -961,7 +1315,7 @@
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -973,7 +1327,7 @@
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -985,7 +1339,7 @@
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -997,7 +1351,7 @@
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -1009,7 +1363,7 @@
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -1027,43 +1381,32 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
-</worksheet>
 </file>
--- a/40_数据库/学习笔记_连接工具_DBeaver.xlsx
+++ b/40_数据库/学习笔记_连接工具_DBeaver.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B72812-8960-44C8-B495-B262A5623C13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD387F48-0170-497C-855F-4B2D0A96A231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <r>
       <rPr>
@@ -155,10 +155,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Dbeaver</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Dbeaver支持跨库导出导入</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -175,15 +171,62 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>不自动生成列</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>启用多行插入</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>提高效率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用多行值插入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DBeaver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://dbeaver.io/download/</t>
+  </si>
+  <si>
+    <t>官网：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DBeaver Community</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>社区版</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>传输不自动生成的列</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不选中，防止修改表结构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>替换方法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ON CONFLICT DO NOTHING</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ON CONFLICT DO UPDATE SET</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冲突时啥也不做</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冲突时更新数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>注：有时选中【使用多行值插入】会报错，可取消选中该项，即一行行写入，虽然有点慢，但能保证成功！！</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -191,7 +234,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -276,6 +319,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -318,7 +368,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -341,6 +391,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -462,13 +513,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>44802</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -531,22 +582,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>666750</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:colOff>666751</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>609908</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>640941</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="图片 3">
+        <xdr:cNvPr id="6" name="图片 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3554EA34-6B5B-418D-A25D-980D421B7036}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6D92415-D19B-45B4-84CD-21A6CC4401CC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -569,8 +620,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="666750" y="8162925"/>
-          <a:ext cx="7486958" cy="4829175"/>
+          <a:off x="666751" y="13201650"/>
+          <a:ext cx="7517990" cy="4562475"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -596,6 +647,150 @@
         </a:extLst>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>609908</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="9" name="组合 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83749447-6043-4C42-9CA4-E18E83B04E6F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="666750" y="8705850"/>
+          <a:ext cx="7486958" cy="4829175"/>
+          <a:chOff x="666750" y="8162925"/>
+          <a:chExt cx="7486958" cy="4829175"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="4" name="图片 3">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3554EA34-6B5B-418D-A25D-980D421B7036}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:srcRect/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr bwMode="auto">
+          <a:xfrm>
+            <a:off x="666750" y="8162925"/>
+            <a:ext cx="7486958" cy="4829175"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="190500" algn="tl" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="70000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:extLst>
+            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a14:hiddenFill>
+            </a:ext>
+          </a:extLst>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="7" name="文本框 6">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E944DC6-4CA2-42CC-896F-29F7CEB25ADF}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5286375" y="10448925"/>
+            <a:ext cx="1454244" cy="334451"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+            <a:spAutoFit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr lang="zh-CN" altLang="en-US" sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+                <a:latin typeface="微软雅黑" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+                <a:ea typeface="微软雅黑" panose="020B0503020204020204" pitchFamily="34" charset="-122"/>
+              </a:rPr>
+              <a:t>表示冲突时啥也不做</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -869,7 +1064,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -892,9 +1087,28 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B3" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -922,46 +1136,74 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4CD61A6-959C-4AA8-BC74-0BE9499DAB0E}">
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B4" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="B41" s="9" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="41" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="B41" s="9" t="s">
+      <c r="E41" t="s">
         <v>12</v>
       </c>
-      <c r="E41" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C42" t="s">
+        <v>19</v>
+      </c>
+      <c r="F42" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="C43" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="F44" t="s">
+        <v>22</v>
+      </c>
+      <c r="J44" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="F45" t="s">
+        <v>23</v>
+      </c>
+      <c r="J45" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="C46" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C43" t="s">
-        <v>14</v>
+      <c r="F46" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
